--- a/data/trans_orig/P24F-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P24F-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le gustaría dejar de fumar en 2007</t>
+          <t>Población según si le gustaría dejar de fumar en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21975</t>
+          <t>22442</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6840</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19118</t>
+          <t>19939</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15616</t>
+          <t>15730</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35744</t>
+          <t>36218</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>115589</t>
+          <t>114652</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>150634</t>
+          <t>151402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63812</t>
+          <t>64690</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89375</t>
+          <t>89193</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>188638</t>
+          <t>189653</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>232027</t>
+          <t>232582</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>111471</t>
+          <t>113493</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148257</t>
+          <t>147699</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41003</t>
+          <t>40925</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64154</t>
+          <t>65006</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>161320</t>
+          <t>162511</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>203313</t>
+          <t>204893</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,59%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33772</t>
+          <t>32298</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58418</t>
+          <t>56175</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12953</t>
+          <t>13756</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31261</t>
+          <t>30540</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50604</t>
+          <t>50811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80441</t>
+          <t>80542</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>11251</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28378</t>
+          <t>28576</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16654</t>
+          <t>16255</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18765</t>
+          <t>18766</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39625</t>
+          <t>39710</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124012</t>
+          <t>124928</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162007</t>
+          <t>163173</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58297</t>
+          <t>59340</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87674</t>
+          <t>88207</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>193672</t>
+          <t>194518</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>245205</t>
+          <t>241714</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,16%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>131569</t>
+          <t>131448</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>170240</t>
+          <t>171502</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91078</t>
+          <t>90833</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122253</t>
+          <t>120822</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>229930</t>
+          <t>232699</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>281180</t>
+          <t>282942</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76064</t>
+          <t>75062</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>112001</t>
+          <t>112391</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>27426</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51588</t>
+          <t>50629</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>111086</t>
+          <t>111825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>154433</t>
+          <t>152982</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10682</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63200</t>
+          <t>62858</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>94593</t>
+          <t>92860</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38812</t>
+          <t>37499</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61010</t>
+          <t>60793</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>108484</t>
+          <t>108128</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>146171</t>
+          <t>144926</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103039</t>
+          <t>101165</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137048</t>
+          <t>135442</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69887</t>
+          <t>70943</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94908</t>
+          <t>96953</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182067</t>
+          <t>178901</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>222759</t>
+          <t>222159</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,52%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41811</t>
+          <t>41854</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67975</t>
+          <t>68200</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27235</t>
+          <t>26401</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49787</t>
+          <t>47446</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73469</t>
+          <t>73554</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>106663</t>
+          <t>109042</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13713</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33189</t>
+          <t>32818</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16254</t>
+          <t>16443</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33564</t>
+          <t>34392</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34844</t>
+          <t>33454</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61073</t>
+          <t>59100</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>144732</t>
+          <t>142692</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>183840</t>
+          <t>181670</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>88457</t>
+          <t>89765</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>122685</t>
+          <t>122005</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>240571</t>
+          <t>241017</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>293569</t>
+          <t>291401</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,08%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>121117</t>
+          <t>121582</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>158171</t>
+          <t>159214</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>101239</t>
+          <t>99764</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>134421</t>
+          <t>134641</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>234276</t>
+          <t>233351</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>283277</t>
+          <t>282707</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65711</t>
+          <t>66534</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98549</t>
+          <t>97970</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46042</t>
+          <t>45280</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72140</t>
+          <t>71918</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121684</t>
+          <t>118763</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>162638</t>
+          <t>161368</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41959</t>
+          <t>43728</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>71914</t>
+          <t>72242</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35269</t>
+          <t>36319</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61706</t>
+          <t>62014</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>84722</t>
+          <t>85139</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>123624</t>
+          <t>123453</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>480607</t>
+          <t>480612</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>550754</t>
+          <t>552610</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>274323</t>
+          <t>276896</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>331182</t>
+          <t>330746</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>775717</t>
+          <t>775211</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>868448</t>
+          <t>864450</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>501939</t>
+          <t>505339</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>575240</t>
+          <t>578158</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>330293</t>
+          <t>329135</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>389451</t>
+          <t>387586</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>852732</t>
+          <t>851167</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>946516</t>
+          <t>944458</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>239529</t>
+          <t>239947</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>302795</t>
+          <t>301805</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>133553</t>
+          <t>131120</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>177637</t>
+          <t>175777</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>386331</t>
+          <t>390450</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>459901</t>
+          <t>462901</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le gustaría dejar de fumar en 2012</t>
+          <t>Población según si le gustaría dejar de fumar en 2012 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8317</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8819</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27377</t>
+          <t>27120</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50881</t>
+          <t>51386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20618</t>
+          <t>20691</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43262</t>
+          <t>42436</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54778</t>
+          <t>55444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86489</t>
+          <t>88393</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>170457</t>
+          <t>171775</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>201625</t>
+          <t>202765</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>94527</t>
+          <t>95747</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>118805</t>
+          <t>120583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>270350</t>
+          <t>272242</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>311377</t>
+          <t>310523</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,15%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31651</t>
+          <t>31123</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55961</t>
+          <t>54505</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14787</t>
+          <t>13942</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31634</t>
+          <t>32285</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50577</t>
+          <t>51218</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80252</t>
+          <t>78926</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10521</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8532</t>
+          <t>9558</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13867</t>
+          <t>14111</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43932</t>
+          <t>42988</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73013</t>
+          <t>73734</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20480</t>
+          <t>20805</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42425</t>
+          <t>41961</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71843</t>
+          <t>71144</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108660</t>
+          <t>107351</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>245192</t>
+          <t>245678</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283886</t>
+          <t>286357</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>181942</t>
+          <t>182164</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>214310</t>
+          <t>215257</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>436939</t>
+          <t>436235</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>488146</t>
+          <t>493102</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>71,1%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61815</t>
+          <t>60974</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>96544</t>
+          <t>94135</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44352</t>
+          <t>43900</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72517</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>113817</t>
+          <t>112708</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>156969</t>
+          <t>157331</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6865</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>13259</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35319</t>
+          <t>34222</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>62612</t>
+          <t>62355</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24414</t>
+          <t>23292</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47079</t>
+          <t>47021</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64438</t>
+          <t>65540</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>99699</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170719</t>
+          <t>170148</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>206701</t>
+          <t>205787</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>118916</t>
+          <t>120247</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150507</t>
+          <t>151867</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>299866</t>
+          <t>298259</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>347489</t>
+          <t>348334</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,21%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59950</t>
+          <t>61032</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92644</t>
+          <t>92774</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42207</t>
+          <t>42675</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69389</t>
+          <t>71735</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111769</t>
+          <t>108608</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>151626</t>
+          <t>153692</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22203</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>11786</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11940</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30466</t>
+          <t>28964</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55451</t>
+          <t>53893</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>85328</t>
+          <t>87029</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36775</t>
+          <t>36401</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62989</t>
+          <t>63252</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>98710</t>
+          <t>97441</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>137731</t>
+          <t>138839</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>170858</t>
+          <t>169571</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>208779</t>
+          <t>209332</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>152871</t>
+          <t>153971</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>188145</t>
+          <t>186923</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>334681</t>
+          <t>335756</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>389151</t>
+          <t>389075</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,44%</t>
         </is>
       </c>
     </row>
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>74004</t>
+          <t>73430</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>107472</t>
+          <t>106667</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53973</t>
+          <t>53195</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82995</t>
+          <t>83217</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>133849</t>
+          <t>134800</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>180663</t>
+          <t>180240</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13914</t>
+          <t>13569</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31575</t>
+          <t>33171</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22705</t>
+          <t>22621</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25232</t>
+          <t>25324</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>47798</t>
+          <t>50165</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>186772</t>
+          <t>183707</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>242598</t>
+          <t>240272</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>120730</t>
+          <t>120235</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>168508</t>
+          <t>168334</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>323074</t>
+          <t>319727</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>394681</t>
+          <t>389484</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>789877</t>
+          <t>792481</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>863752</t>
+          <t>866741</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>583909</t>
+          <t>578231</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>646047</t>
+          <t>642317</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1395667</t>
+          <t>1393728</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1490237</t>
+          <t>1490702</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,23%</t>
         </is>
       </c>
     </row>
@@ -6424,12 +6424,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>253111</t>
+          <t>253796</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>314093</t>
+          <t>317323</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>175560</t>
+          <t>177156</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>227924</t>
+          <t>229306</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>447121</t>
+          <t>447113</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>524307</t>
+          <t>526317</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le gustaría dejar de fumar en 2016</t>
+          <t>Población según si le gustaría dejar de fumar en 2016 (tasa de respuesta: 98,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6886,12 +6886,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>841</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19599</t>
+          <t>20161</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -6999,12 +6999,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30543</t>
+          <t>30896</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54796</t>
+          <t>54249</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26994</t>
+          <t>27460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48945</t>
+          <t>48612</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62877</t>
+          <t>63564</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96036</t>
+          <t>97853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -7112,12 +7112,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>132959</t>
+          <t>131857</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>165903</t>
+          <t>162910</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78361</t>
+          <t>77287</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103690</t>
+          <t>103790</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>218196</t>
+          <t>217828</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>259364</t>
+          <t>258037</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,04%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38959</t>
+          <t>41924</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66195</t>
+          <t>67986</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25008</t>
+          <t>24855</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46222</t>
+          <t>46602</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70550</t>
+          <t>71490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104735</t>
+          <t>106616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22813</t>
+          <t>22662</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17576</t>
+          <t>17968</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15934</t>
+          <t>16449</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>35207</t>
+          <t>35030</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -7568,12 +7568,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41672</t>
+          <t>41306</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69104</t>
+          <t>69264</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7583,12 +7583,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34305</t>
+          <t>33855</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58015</t>
+          <t>57923</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>80494</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117819</t>
+          <t>118841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -7681,12 +7681,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>181539</t>
+          <t>180424</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>216960</t>
+          <t>215297</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154440</t>
+          <t>152626</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>185335</t>
+          <t>185388</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>345908</t>
+          <t>345297</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>391381</t>
+          <t>392267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,64%</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47670</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76797</t>
+          <t>77333</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32612</t>
+          <t>32128</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58126</t>
+          <t>57145</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>86702</t>
+          <t>85271</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>123979</t>
+          <t>124774</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>16714</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8039,12 +8039,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19789</t>
+          <t>19245</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -8137,12 +8137,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57111</t>
+          <t>56580</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88732</t>
+          <t>87403</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>53932</t>
+          <t>54945</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>81885</t>
+          <t>81565</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>120231</t>
+          <t>118822</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>161841</t>
+          <t>162928</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>119604</t>
+          <t>122489</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157689</t>
+          <t>157962</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89046</t>
+          <t>88662</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118928</t>
+          <t>117379</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>217915</t>
+          <t>216470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>265057</t>
+          <t>262777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>49,96%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68642</t>
+          <t>69612</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101429</t>
+          <t>101410</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38789</t>
+          <t>38864</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66562</t>
+          <t>64672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>115738</t>
+          <t>115857</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>155202</t>
+          <t>156981</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14423</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16053</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48373</t>
+          <t>48354</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>75858</t>
+          <t>77638</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23941</t>
+          <t>23918</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46601</t>
+          <t>46703</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>79210</t>
+          <t>78877</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115777</t>
+          <t>114524</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>146541</t>
+          <t>148553</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>178614</t>
+          <t>180323</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>141441</t>
+          <t>143255</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>173154</t>
+          <t>173119</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8889,12 +8889,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>299800</t>
+          <t>298850</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>344274</t>
+          <t>344624</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,15%</t>
         </is>
       </c>
     </row>
@@ -8932,12 +8932,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41788</t>
+          <t>41866</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67464</t>
+          <t>70352</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43411</t>
+          <t>44006</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70746</t>
+          <t>71084</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91406</t>
+          <t>92607</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>128279</t>
+          <t>130188</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22930</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46452</t>
+          <t>46625</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>42513</t>
+          <t>42262</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>72600</t>
+          <t>71243</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -9275,12 +9275,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>199312</t>
+          <t>204103</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>259409</t>
+          <t>260841</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>158616</t>
+          <t>159086</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>208637</t>
+          <t>208274</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9345,12 +9345,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>374471</t>
+          <t>374979</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>452268</t>
+          <t>449093</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>614349</t>
+          <t>612150</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>682997</t>
+          <t>681503</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>491422</t>
+          <t>491200</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>551755</t>
+          <t>551729</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1128989</t>
+          <t>1122715</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1218215</t>
+          <t>1214632</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9473,12 +9473,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,49%</t>
         </is>
       </c>
     </row>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>222344</t>
+          <t>219290</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>277521</t>
+          <t>280960</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>159466</t>
+          <t>162480</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>212258</t>
+          <t>210310</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>397162</t>
+          <t>400894</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>473711</t>
+          <t>476394</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24F-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P24F-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22442</t>
+          <t>21853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>19964</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>15959</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36218</t>
+          <t>36471</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>114652</t>
+          <t>116408</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>151402</t>
+          <t>150516</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64690</t>
+          <t>64196</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89193</t>
+          <t>88139</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>189653</t>
+          <t>188930</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>232582</t>
+          <t>231898</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,2%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>113493</t>
+          <t>113232</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>147699</t>
+          <t>147653</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40925</t>
+          <t>41271</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65006</t>
+          <t>64125</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>162511</t>
+          <t>163643</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>204893</t>
+          <t>203047</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,21%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32298</t>
+          <t>32308</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56175</t>
+          <t>58018</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13756</t>
+          <t>13179</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30540</t>
+          <t>30225</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50811</t>
+          <t>50216</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80542</t>
+          <t>80663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11251</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28576</t>
+          <t>29055</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16255</t>
+          <t>16789</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18766</t>
+          <t>18112</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39710</t>
+          <t>39614</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124928</t>
+          <t>124922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>163173</t>
+          <t>164347</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59340</t>
+          <t>59428</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88207</t>
+          <t>88719</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>194518</t>
+          <t>193647</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>241714</t>
+          <t>242125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>131448</t>
+          <t>130612</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>171502</t>
+          <t>171209</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90833</t>
+          <t>90121</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120822</t>
+          <t>121470</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>232699</t>
+          <t>231684</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>282942</t>
+          <t>282608</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75062</t>
+          <t>77430</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>112391</t>
+          <t>112505</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27426</t>
+          <t>27926</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50629</t>
+          <t>50947</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>111825</t>
+          <t>110623</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152982</t>
+          <t>151729</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6899</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62858</t>
+          <t>63107</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92860</t>
+          <t>92834</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37499</t>
+          <t>38260</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>60793</t>
+          <t>61224</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>108128</t>
+          <t>106866</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>144926</t>
+          <t>144088</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101165</t>
+          <t>101076</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135442</t>
+          <t>134209</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70943</t>
+          <t>69753</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96953</t>
+          <t>95058</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>178901</t>
+          <t>181106</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>222159</t>
+          <t>222551</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41854</t>
+          <t>42310</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68200</t>
+          <t>68070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26401</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47446</t>
+          <t>49116</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73554</t>
+          <t>75109</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>109042</t>
+          <t>110410</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>13771</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32818</t>
+          <t>32886</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16443</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34392</t>
+          <t>34377</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33454</t>
+          <t>32720</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59100</t>
+          <t>60540</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>142692</t>
+          <t>142533</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>181670</t>
+          <t>181152</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89765</t>
+          <t>86979</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>122005</t>
+          <t>121273</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>241017</t>
+          <t>241175</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>291401</t>
+          <t>295103</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,61%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>121582</t>
+          <t>122074</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>159214</t>
+          <t>159966</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>99764</t>
+          <t>99520</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>134641</t>
+          <t>134597</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>233351</t>
+          <t>235740</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>282707</t>
+          <t>282868</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66534</t>
+          <t>67571</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97970</t>
+          <t>98593</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45280</t>
+          <t>46585</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71918</t>
+          <t>73014</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>118763</t>
+          <t>118853</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>161368</t>
+          <t>160789</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43728</t>
+          <t>42325</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>72242</t>
+          <t>72463</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36319</t>
+          <t>34837</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>62014</t>
+          <t>61009</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>85139</t>
+          <t>85318</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>123453</t>
+          <t>125985</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>480612</t>
+          <t>481172</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>552610</t>
+          <t>555753</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>276896</t>
+          <t>272821</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>330746</t>
+          <t>329354</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>775211</t>
+          <t>775466</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>864450</t>
+          <t>866010</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>505339</t>
+          <t>503800</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>578158</t>
+          <t>577745</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>329135</t>
+          <t>329903</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>387586</t>
+          <t>387843</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>851167</t>
+          <t>854570</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>944458</t>
+          <t>950365</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>239947</t>
+          <t>240708</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>301805</t>
+          <t>300911</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>131120</t>
+          <t>132167</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>175777</t>
+          <t>177644</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>390450</t>
+          <t>387870</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>462901</t>
+          <t>463161</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>27876</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51386</t>
+          <t>51984</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20691</t>
+          <t>21121</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42436</t>
+          <t>42307</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55444</t>
+          <t>53576</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88393</t>
+          <t>86520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>171775</t>
+          <t>169169</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>202765</t>
+          <t>201357</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>95747</t>
+          <t>93577</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>120583</t>
+          <t>119802</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>272242</t>
+          <t>272789</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>310523</t>
+          <t>313225</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,78%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31123</t>
+          <t>31267</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54505</t>
+          <t>55765</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13942</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32285</t>
+          <t>31252</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51218</t>
+          <t>50656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78926</t>
+          <t>80061</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10521</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14111</t>
+          <t>14656</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42988</t>
+          <t>44510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73734</t>
+          <t>75870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20805</t>
+          <t>20348</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41961</t>
+          <t>42998</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71144</t>
+          <t>69525</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107351</t>
+          <t>106567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>245678</t>
+          <t>246410</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>286357</t>
+          <t>282988</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>182164</t>
+          <t>179789</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>215257</t>
+          <t>214380</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>436235</t>
+          <t>438494</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>493102</t>
+          <t>487852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,34%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60974</t>
+          <t>61113</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94135</t>
+          <t>94064</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43900</t>
+          <t>45425</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71899</t>
+          <t>73372</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112708</t>
+          <t>113631</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>157331</t>
+          <t>156533</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10064</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>13010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34222</t>
+          <t>34582</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>62355</t>
+          <t>60686</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23292</t>
+          <t>23944</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47021</t>
+          <t>45413</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>65540</t>
+          <t>65836</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>98981</t>
+          <t>100391</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170148</t>
+          <t>171892</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>205787</t>
+          <t>207124</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>120323</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>151867</t>
+          <t>151100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>298259</t>
+          <t>301841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>348334</t>
+          <t>351093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,72%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61032</t>
+          <t>60755</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92774</t>
+          <t>91751</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42675</t>
+          <t>42208</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71735</t>
+          <t>70643</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>108608</t>
+          <t>110066</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>153692</t>
+          <t>151691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>7506</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22573</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11786</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12439</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28964</t>
+          <t>31135</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53893</t>
+          <t>53873</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>87029</t>
+          <t>84415</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36401</t>
+          <t>37592</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63252</t>
+          <t>64157</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>97441</t>
+          <t>99335</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>138839</t>
+          <t>142793</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>169571</t>
+          <t>172438</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>209332</t>
+          <t>208970</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>153971</t>
+          <t>153058</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>186923</t>
+          <t>187266</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>335756</t>
+          <t>333685</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>389075</t>
+          <t>385113</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>58,84%</t>
         </is>
       </c>
     </row>
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73430</t>
+          <t>74513</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106667</t>
+          <t>106122</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53195</t>
+          <t>54517</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>83217</t>
+          <t>83380</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>134800</t>
+          <t>134488</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>180240</t>
+          <t>179242</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13569</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33171</t>
+          <t>33475</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25324</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50165</t>
+          <t>48169</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>183707</t>
+          <t>185735</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>240272</t>
+          <t>240356</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>120235</t>
+          <t>121677</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>168334</t>
+          <t>167330</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>319727</t>
+          <t>319466</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>389484</t>
+          <t>392662</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>792481</t>
+          <t>792612</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>866741</t>
+          <t>867469</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>578231</t>
+          <t>581987</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>642317</t>
+          <t>644571</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1393728</t>
+          <t>1390516</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1490702</t>
+          <t>1486904</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,06%</t>
         </is>
       </c>
     </row>
@@ -6424,12 +6424,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>253796</t>
+          <t>254205</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>317323</t>
+          <t>314631</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>177156</t>
+          <t>176116</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>229306</t>
+          <t>230053</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>447113</t>
+          <t>448551</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>526317</t>
+          <t>533812</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -6886,12 +6886,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15229</t>
+          <t>15196</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>826</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>9776</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20161</t>
+          <t>19601</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -6999,12 +6999,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30896</t>
+          <t>29486</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54249</t>
+          <t>52716</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27460</t>
+          <t>27088</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48612</t>
+          <t>48847</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63564</t>
+          <t>63716</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97853</t>
+          <t>95268</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -7112,12 +7112,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>131857</t>
+          <t>132461</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>162910</t>
+          <t>163516</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77287</t>
+          <t>79268</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103790</t>
+          <t>104314</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>217828</t>
+          <t>220841</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>258037</t>
+          <t>261070</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,77%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41924</t>
+          <t>41490</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67986</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24855</t>
+          <t>25138</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46602</t>
+          <t>46552</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71490</t>
+          <t>68538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106616</t>
+          <t>102226</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>22582</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17968</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>35030</t>
+          <t>36010</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -7568,12 +7568,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41306</t>
+          <t>41644</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69264</t>
+          <t>70850</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7583,12 +7583,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33855</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57923</t>
+          <t>58840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80494</t>
+          <t>78748</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118841</t>
+          <t>117880</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -7681,12 +7681,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>180424</t>
+          <t>178465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>215297</t>
+          <t>216496</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152626</t>
+          <t>153805</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>185388</t>
+          <t>185841</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>345297</t>
+          <t>344667</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>392267</t>
+          <t>394084</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,95%</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47633</t>
+          <t>46703</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77333</t>
+          <t>78576</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32128</t>
+          <t>31468</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57145</t>
+          <t>56355</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85271</t>
+          <t>84974</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124774</t>
+          <t>126559</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16714</t>
+          <t>17759</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8039,12 +8039,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6661</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19245</t>
+          <t>19737</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -8137,12 +8137,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56580</t>
+          <t>56862</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>87403</t>
+          <t>90026</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54945</t>
+          <t>55846</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>81565</t>
+          <t>80312</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>118822</t>
+          <t>117073</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>162928</t>
+          <t>160193</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>122489</t>
+          <t>121008</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157962</t>
+          <t>157617</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>88662</t>
+          <t>88123</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>117379</t>
+          <t>116500</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>216470</t>
+          <t>218269</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>262777</t>
+          <t>265649</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,5%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69612</t>
+          <t>68364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101410</t>
+          <t>100946</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38864</t>
+          <t>39228</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64672</t>
+          <t>63807</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>115857</t>
+          <t>115472</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>156981</t>
+          <t>155996</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15023</t>
+          <t>17008</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48354</t>
+          <t>48234</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77638</t>
+          <t>75460</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23918</t>
+          <t>25314</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46703</t>
+          <t>45925</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78877</t>
+          <t>79538</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>114524</t>
+          <t>117462</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>148553</t>
+          <t>147094</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>180323</t>
+          <t>178681</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>143255</t>
+          <t>143101</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>173119</t>
+          <t>173597</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8889,12 +8889,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>298850</t>
+          <t>296774</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>344624</t>
+          <t>344057</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,05%</t>
         </is>
       </c>
     </row>
@@ -8932,12 +8932,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41866</t>
+          <t>42647</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70352</t>
+          <t>68402</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44006</t>
+          <t>43980</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71084</t>
+          <t>70762</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92607</t>
+          <t>91465</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>130188</t>
+          <t>130618</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22748</t>
+          <t>23438</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46625</t>
+          <t>46624</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14646</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33681</t>
+          <t>34599</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>42262</t>
+          <t>43597</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>71243</t>
+          <t>73105</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -9275,12 +9275,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>204103</t>
+          <t>201590</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>260841</t>
+          <t>259692</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>159086</t>
+          <t>160201</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>208035</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9345,12 +9345,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>374979</t>
+          <t>372805</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>449093</t>
+          <t>448824</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>612150</t>
+          <t>611752</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>681503</t>
+          <t>683084</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>491200</t>
+          <t>490928</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>551729</t>
+          <t>552543</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1122715</t>
+          <t>1126482</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1214632</t>
+          <t>1219628</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9473,12 +9473,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,73%</t>
         </is>
       </c>
     </row>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>219290</t>
+          <t>223984</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>280960</t>
+          <t>278454</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>162480</t>
+          <t>159183</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>210310</t>
+          <t>211036</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>400894</t>
+          <t>398439</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>476394</t>
+          <t>480744</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
